--- a/china-coal/数据源/中煤能源_月度经营数据.xlsx
+++ b/china-coal/数据源/中煤能源_月度经营数据.xlsx
@@ -1,31 +1,225 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="煤炭业务月度数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="煤化工与煤矿装备月度数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="煤炭业务月度数据" sheetId="1" r:id="rId3"/>
+    <sheet name="煤化工与煤矿装备月度数据" sheetId="2" r:id="rId4"/>
+    <sheet name="数据说明" sheetId="3" r:id="rId5"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <r>
+      <t>月份</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>商品煤产量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>商品煤销量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>自产商品煤销量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>商品煤产量（2025，万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>商品煤销量（2025，万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>自产商品煤销量（2025，万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年1月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年2月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年3月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年4月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年5月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年6月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2026年7月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1-7月累计</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>聚乙烯产量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>聚丙烯产量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>甲醇产量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>硝铵产量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>尿素产量（万吨）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>煤矿装备产值（亿元）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>聚乙烯产量（2025）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>聚丙烯产量（2025）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>甲醇产量（2025）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>硝铵产量（2025）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>尿素产量（2025）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>煤矿装备产值（2025，亿元）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>数据说明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. 数据来源：中煤能源（601898.SH / 01898.HK）2026年1-7月各月《主要生产经营数据公告》；表中另含各指标 2025年同期（2025年1-7月单月）列，同源。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 统计口径：公司合并报表口径，覆盖所有控股并表矿区与生产基地</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. 商品煤销量为全口径，包含自产商品煤、买断贸易煤、进出口及代理业务</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. 尿素产量：各月公告均单独披露，2026年1-7月已补全（原“部分月份未披露”说明已不适用）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. 数据为公司初步核算数，最终值以定期报告为准</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. 2025年列仅作同比对照；月度趋势图（build_monthly_svg.py）只取 2026 年列，不受新增列影响。</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="300" formatCode="General"/>
+    <numFmt numFmtId="301" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -38,8 +232,15 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,12 +249,28 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -68,99 +285,49 @@
       <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="6" fillId="3" borderId="2" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="300" fontId="6" fillId="3" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="300" fontId="6" fillId="3" borderId="2" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="300" fontId="6" fillId="3" borderId="2" xfId="0"/>
+    <xf numFmtId="301" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="6" fillId="3" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="0" fillId="0" borderId="3" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -453,163 +620,256 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>商品煤产量（万吨）</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>商品煤销量（万吨）</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>自产商品煤销量（万吨）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026年1月</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5">
         <v>1029</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5">
         <v>2005</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="5">
         <v>1057</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026年2月</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="3" spans="1:4">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5">
         <v>891</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5">
         <v>1651</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="5">
         <v>865</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026年3月</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="4" spans="1:4">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5">
         <v>1097</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5">
         <v>1946</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="5">
         <v>1048</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026年4月</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+    <row r="5" spans="1:4">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5">
         <v>1002</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="5">
         <v>2042</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="5">
         <v>1029</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026年5月</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+    <row r="6" spans="1:4">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5">
         <v>1081</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5">
         <v>2187</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="5">
         <v>1051</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026年6月</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+    <row r="7" spans="1:4">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
         <v>1095</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5">
         <v>2147</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="5">
         <v>1092</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026年7月</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
         <v>1081</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="5">
         <v>2063</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="5">
         <v>1114</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>1-7月累计</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
+    <row r="9" spans="1:4">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6">
         <v>7276</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="6">
         <v>14033</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="6">
         <v>7256</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="11" t="s"/>
+      <c r="C15" s="11" t="s"/>
+      <c r="D15" s="11" t="s"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="10">
+        <v>45658</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1148</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2163</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="10">
+        <v>45689</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1024</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1747</v>
+      </c>
+      <c r="D17" s="5">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="10">
+        <v>45717</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1163</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2476</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="10">
+        <v>45748</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1105</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2110</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="10">
+        <v>45778</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1190</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2179</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="10">
+        <v>45809</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1104</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2165</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="10">
+        <v>45839</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1105</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2117</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="6">
+        <v>7839</v>
+      </c>
+      <c r="C23" s="6">
+        <v>14985</v>
+      </c>
+      <c r="D23" s="6">
+        <v>7889</v>
       </c>
     </row>
   </sheetData>
@@ -623,220 +883,361 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="19.0898" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>聚乙烯产量（万吨）</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>聚丙烯产量（万吨）</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>甲醇产量（万吨）</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>硝铵产量（万吨）</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>尿素产量（万吨）</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>煤矿装备产值（亿元）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026年1月</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5">
         <v>6.6</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5">
         <v>6.3</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="5">
         <v>18.3</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="5">
         <v>5.5</v>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n">
+      <c r="F2" s="5">
+        <v>18.4</v>
+      </c>
+      <c r="G2" s="5">
         <v>7.7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026年2月</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5">
         <v>6.1</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5">
         <v>5.7</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="D3" s="5">
+        <v>17.1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="F3" s="5">
         <v>16.6</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="5">
         <v>5.6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026年3月</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="4" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5">
         <v>6.7</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5">
+        <v>6.2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>16.6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5">
+        <v>18.7</v>
+      </c>
+      <c r="G4" s="5">
+        <v>8.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>6.5</v>
+      </c>
+      <c r="D5" s="5">
+        <v>14.1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>18.2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>6.3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>15.2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3.9</v>
+      </c>
+      <c r="F6" s="5">
+        <v>13.6</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="C7" s="5">
+        <v>6.4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>17.1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>4.9</v>
+      </c>
+      <c r="F7" s="5">
+        <v>16.8</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>6.3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>17.7</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4.7</v>
+      </c>
+      <c r="F8" s="5">
+        <v>18.4</v>
+      </c>
+      <c r="G8" s="5">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="12">
+        <v>45658</v>
+      </c>
+      <c r="B15" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="C15" s="5">
+        <v>6.3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>17.8</v>
+      </c>
+      <c r="E15" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="F15" s="5">
+        <v>17.9</v>
+      </c>
+      <c r="G15" s="5">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="12">
+        <v>45689</v>
+      </c>
+      <c r="B16" s="5">
         <v>5.9</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="C16" s="5">
+        <v>5.7</v>
+      </c>
+      <c r="D16" s="5">
+        <v>16.4</v>
+      </c>
+      <c r="E16" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="F16" s="5">
+        <v>16.2</v>
+      </c>
+      <c r="G16" s="5">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12">
+        <v>45717</v>
+      </c>
+      <c r="B17" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="C17" s="5">
+        <v>6.5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>17.2</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5.9</v>
+      </c>
+      <c r="F17" s="5">
+        <v>18.7</v>
+      </c>
+      <c r="G17" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12">
+        <v>45748</v>
+      </c>
+      <c r="B18" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="C18" s="5">
+        <v>6.4</v>
+      </c>
+      <c r="D18" s="5">
+        <v>16.6</v>
+      </c>
+      <c r="E18" s="5">
+        <v>5.3</v>
+      </c>
+      <c r="F18" s="5">
+        <v>18.1</v>
+      </c>
+      <c r="G18" s="5">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="12">
+        <v>45778</v>
+      </c>
+      <c r="B19" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>16.9</v>
+      </c>
+      <c r="E19" s="5">
+        <v>6</v>
+      </c>
+      <c r="F19" s="5">
+        <v>18.6</v>
+      </c>
+      <c r="G19" s="5">
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12">
+        <v>45809</v>
+      </c>
+      <c r="B20" s="5">
         <v>3.9</v>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026年4月</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026年5月</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026年6月</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026年7月</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>5.5</v>
+      <c r="C20" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>13.3</v>
+      </c>
+      <c r="E20" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="F20" s="5">
+        <v>15.1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="12">
+        <v>45839</v>
+      </c>
+      <c r="B21" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="D21" s="5">
+        <v>16.9</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4</v>
+      </c>
+      <c r="F21" s="5">
+        <v>18.6</v>
+      </c>
+      <c r="G21" s="5">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -850,52 +1251,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>数据说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>1. 数据来源：中煤能源（601898.SH / 01898.HK）2026年1-7月各月《主要生产经营数据公告》</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>2. 统计口径：公司合并报表口径，覆盖所有控股并表矿区与生产基地</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>3. 商品煤销量为全口径，包含自产商品煤、买断贸易煤、进出口及代理业务</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>4. 部分月份尿素产量未在单月公告中单独披露，故留空</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>5. 数据为公司初步核算数，最终值以定期报告为准</t>
-        </is>
+    <row r="1" spans="1:1">
+      <c r="A1" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="9" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/china-coal/数据源/中煤能源_月度经营数据.xlsx
+++ b/china-coal/数据源/中煤能源_月度经营数据.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t/>
   </si>
@@ -42,21 +42,6 @@
   </si>
   <si>
     <r>
-      <t>商品煤产量（2025，万吨）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>商品煤销量（2025，万吨）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>自产商品煤销量（2025，万吨）</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>2026年1月</t>
     </r>
   </si>
@@ -92,7 +77,12 @@
   </si>
   <si>
     <r>
-      <t>1-7月累计</t>
+      <t>2026年8月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1-8月累计</t>
     </r>
   </si>
   <si>
@@ -127,42 +117,12 @@
   </si>
   <si>
     <r>
-      <t>聚乙烯产量（2025）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>聚丙烯产量（2025）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>甲醇产量（2025）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>硝铵产量（2025）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>尿素产量（2025）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>煤矿装备产值（2025，亿元）</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>数据说明</t>
     </r>
   </si>
   <si>
     <r>
-      <t>1. 数据来源：中煤能源（601898.SH / 01898.HK）2026年1-7月各月《主要生产经营数据公告》；表中另含各指标 2025年同期（2025年1-7月单月）列，同源。</t>
+      <t>1. 数据来源：中煤能源（601898.SH / 01898.HK）2026年1-8月各月《主要生产经营数据公告》；表中另含各指标 2025年同期（2025年1-8月单月）列，同源。</t>
     </r>
   </si>
   <si>
@@ -195,9 +155,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="300" formatCode="General"/>
-    <numFmt numFmtId="301" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
+  <numFmts count="3">
+    <numFmt numFmtId="300" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
+    <numFmt numFmtId="301" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="302" formatCode="General"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -226,18 +187,18 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -283,12 +244,13 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs>
-    <xf numFmtId="300" fontId="6" fillId="3" borderId="2" xfId="0"/>
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="2" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -299,31 +261,39 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="302" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="6" fillId="3" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="302" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="300" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="302" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="6" fillId="3" borderId="2" xfId="0" applyAlignment="1">
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="2" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="6" fillId="3" borderId="2" xfId="0"/>
-    <xf numFmtId="301" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="2" xfId="0"/>
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="300" fontId="6" fillId="3" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="300" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="301" fontId="0" fillId="0" borderId="3" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="302" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,13 +590,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="D23"/>
+  <dimension ref="D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="1" max="1" width="14" style="16" customWidth="1"/>
+    <col min="2" max="2" width="20" style="16" customWidth="1"/>
+    <col min="3" max="3" width="20" style="16" customWidth="1"/>
+    <col min="4" max="4" width="22" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -645,7 +615,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5">
         <v>1029</v>
@@ -659,7 +629,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5">
         <v>891</v>
@@ -673,7 +643,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5">
         <v>1097</v>
@@ -687,7 +657,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5">
         <v>1002</v>
@@ -701,7 +671,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="5">
         <v>1081</v>
@@ -715,7 +685,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5">
         <v>1095</v>
@@ -729,7 +699,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="5">
         <v>1081</v>
@@ -742,134 +712,162 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="6">
-        <v>7276</v>
-      </c>
-      <c r="C9" s="6">
-        <v>14033</v>
-      </c>
-      <c r="D9" s="6">
-        <v>7256</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="B15" s="11" t="s"/>
-      <c r="C15" s="11" t="s"/>
-      <c r="D15" s="11" t="s"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="10">
+      <c r="A9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1008</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2139</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="7">
+        <v>8284</v>
+      </c>
+      <c r="C10" s="7">
+        <v>16172</v>
+      </c>
+      <c r="D10" s="7">
+        <v>8299</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="B16" s="5" t="s"/>
+      <c r="C16" s="5" t="s"/>
+      <c r="D16" s="5" t="s"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="8">
         <v>45658</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="5">
         <v>1148</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C17" s="5">
         <v>2163</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D17" s="5">
         <v>1039</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="10">
+    <row r="18" spans="1:4">
+      <c r="A18" s="8">
         <v>45689</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B18" s="5">
         <v>1024</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C18" s="5">
         <v>1747</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D18" s="5">
         <v>962</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="10">
+    <row r="19" spans="1:4">
+      <c r="A19" s="8">
         <v>45717</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B19" s="5">
         <v>1163</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C19" s="5">
         <v>2476</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D19" s="5">
         <v>1239</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="10">
+    <row r="20" spans="1:4">
+      <c r="A20" s="8">
         <v>45748</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B20" s="5">
         <v>1105</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C20" s="5">
         <v>2110</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D20" s="5">
         <v>1114</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="10">
+    <row r="21" spans="1:4">
+      <c r="A21" s="8">
         <v>45778</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B21" s="5">
         <v>1190</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C21" s="5">
         <v>2179</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D21" s="5">
         <v>1176</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="10">
+    <row r="22" spans="1:4">
+      <c r="A22" s="8">
         <v>45809</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B22" s="5">
         <v>1104</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C22" s="5">
         <v>2165</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D22" s="5">
         <v>1153</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="10">
+    <row r="23" spans="1:4">
+      <c r="A23" s="8">
         <v>45839</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B23" s="5">
         <v>1105</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C23" s="5">
         <v>2117</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D23" s="5">
         <v>1178</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="6">
-        <v>7839</v>
-      </c>
-      <c r="C23" s="6">
-        <v>14985</v>
-      </c>
-      <c r="D23" s="6">
-        <v>7889</v>
+    <row r="24" spans="1:4">
+      <c r="A24" s="9">
+        <v>45870</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1160</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2085</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="7">
+        <v>8999</v>
+      </c>
+      <c r="C25" s="7">
+        <v>17070</v>
+      </c>
+      <c r="D25" s="7">
+        <v>9040</v>
       </c>
     </row>
   </sheetData>
@@ -883,16 +881,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="G21"/>
+  <dimension ref="G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="19.0898" customWidth="1"/>
+    <col min="1" max="1" width="16" style="16" customWidth="1"/>
+    <col min="2" max="2" width="16" style="16" customWidth="1"/>
+    <col min="3" max="3" width="16" style="16" customWidth="1"/>
+    <col min="4" max="4" width="16" style="16" customWidth="1"/>
+    <col min="5" max="5" width="16" style="16" customWidth="1"/>
+    <col min="6" max="6" width="16" style="16" customWidth="1"/>
+    <col min="7" max="7" width="19.0898" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -900,27 +898,27 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5">
         <v>6.6</v>
@@ -943,7 +941,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" s="5">
         <v>6.1</v>
@@ -966,7 +964,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5">
         <v>6.7</v>
@@ -989,7 +987,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="5">
         <v>6.6</v>
@@ -1012,7 +1010,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="5">
         <v>6.7</v>
@@ -1035,7 +1033,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5">
         <v>6.7</v>
@@ -1058,7 +1056,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" s="5">
         <v>6.6</v>
@@ -1079,164 +1077,210 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="12">
+    <row r="9" spans="1:7">
+      <c r="A9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="14">
+        <v>6.8</v>
+      </c>
+      <c r="C9" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="D9" s="14">
+        <v>17.4</v>
+      </c>
+      <c r="E9" s="14">
+        <v>5</v>
+      </c>
+      <c r="F9" s="14">
+        <v>18.6</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="10">
         <v>45658</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B16" s="5">
         <v>6.7</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C16" s="5">
         <v>6.3</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D16" s="5">
         <v>17.8</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E16" s="5">
         <v>4.3</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F16" s="5">
         <v>17.9</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G16" s="5">
         <v>8.3</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="12">
+    <row r="17" spans="1:7">
+      <c r="A17" s="10">
         <v>45689</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="5">
         <v>5.9</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C17" s="5">
         <v>5.7</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D17" s="5">
         <v>16.4</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E17" s="5">
         <v>3.7</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F17" s="5">
         <v>16.2</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G17" s="5">
         <v>7.9</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="12">
+    <row r="18" spans="1:7">
+      <c r="A18" s="10">
         <v>45717</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B18" s="5">
         <v>6.7</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C18" s="5">
         <v>6.5</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D18" s="5">
         <v>17.2</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E18" s="5">
         <v>5.9</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F18" s="5">
         <v>18.7</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G18" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="12">
+    <row r="19" spans="1:7">
+      <c r="A19" s="10">
         <v>45748</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B19" s="5">
         <v>6.6</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C19" s="5">
         <v>6.4</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D19" s="5">
         <v>16.6</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E19" s="5">
         <v>5.3</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F19" s="5">
         <v>18.1</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G19" s="5">
         <v>7.9</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="12">
+    <row r="20" spans="1:7">
+      <c r="A20" s="10">
         <v>45778</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B20" s="5">
         <v>4.8</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C20" s="5">
         <v>4.1</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D20" s="5">
         <v>16.9</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E20" s="5">
         <v>6</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F20" s="5">
         <v>18.6</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G20" s="5">
         <v>8.3</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="12">
+    <row r="21" spans="1:7">
+      <c r="A21" s="10">
         <v>45809</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B21" s="5">
         <v>3.9</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C21" s="5">
         <v>3.1</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D21" s="5">
         <v>13.3</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E21" s="5">
         <v>4.1</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F21" s="5">
         <v>15.1</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G21" s="5">
         <v>7.8</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="12">
+    <row r="22" spans="1:7">
+      <c r="A22" s="10">
         <v>45839</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B22" s="5">
         <v>3.2</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C22" s="5">
         <v>3.3</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D22" s="5">
         <v>16.9</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E22" s="5">
         <v>4</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F22" s="5">
         <v>18.6</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G22" s="5">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="15">
+        <v>45870</v>
+      </c>
+      <c r="B23" s="14">
+        <v>6.7</v>
+      </c>
+      <c r="C23" s="14">
+        <v>6.4</v>
+      </c>
+      <c r="D23" s="14">
+        <v>16.6</v>
+      </c>
+      <c r="E23" s="14">
+        <v>4.7</v>
+      </c>
+      <c r="F23" s="14">
+        <v>18.3</v>
+      </c>
+      <c r="G23" s="14">
         <v>7.9</v>
       </c>
     </row>
@@ -1254,42 +1298,42 @@
   <dimension ref="A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="80" customWidth="1"/>
+    <col min="1" max="1" width="80" style="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
-        <v>28</v>
+      <c r="A1" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="8" t="s">
-        <v>29</v>
+      <c r="A2" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="8" t="s">
-        <v>30</v>
+      <c r="A3" s="12" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="8" t="s">
-        <v>31</v>
+      <c r="A4" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="8" t="s">
-        <v>32</v>
+      <c r="A5" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="8" t="s">
-        <v>33</v>
+      <c r="A6" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="9" t="s">
-        <v>34</v>
+      <c r="A7" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
